--- a/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/Private Assets Investing.xlsx
+++ b/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/Private Assets Investing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFC636F-2546-B447-9F78-AA2A9C8AA720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236615EE-30A7-C74D-8494-52B5F229817A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2060" yWindow="760" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{98DD0C7C-FC4E-7943-83E9-6FD42A55B3FD}"/>
+    <workbookView xWindow="26680" yWindow="1900" windowWidth="28040" windowHeight="17440" activeTab="3" xr2:uid="{98DD0C7C-FC4E-7943-83E9-6FD42A55B3FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Buyout Fund" sheetId="2" r:id="rId1"/>
@@ -471,12 +471,6 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -498,6 +492,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3327,7 +3327,17 @@
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.9394215170339894E-2"/>
+          <c:y val="0.13831073199183436"/>
+          <c:w val="0.87375486355662824"/>
+          <c:h val="0.75466025080198307"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="stacked"/>
@@ -3335,6 +3345,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Flows!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Buyout</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -3423,6 +3444,17 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Flows!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Private Credit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent2"/>
@@ -3511,6 +3543,17 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Flows!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Buyout</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent3"/>
@@ -3599,6 +3642,17 @@
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Flows!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Private Credit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="accent4"/>
@@ -3709,14 +3763,12 @@
         <c:tickLblPos val="low"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
+              <a:schemeClr val="dk1"/>
             </a:solidFill>
-            <a:round/>
+            <a:prstDash val="solid"/>
+            <a:miter lim="800000"/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -3732,7 +3784,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Aptos Light" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -3774,8 +3826,12 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:miter lim="800000"/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -3791,7 +3847,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Aptos Light" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -3812,7 +3868,15 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3833,7 +3897,7 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Aptos Light" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -3854,16 +3918,9 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:noFill/>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -3873,7 +3930,9 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr b="0" i="0">
+          <a:latin typeface="Aptos Light" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -6771,16 +6830,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>577850</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>730250</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>241300</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7137,11 +7196,11 @@
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3" t="s">
@@ -16659,80 +16718,80 @@
     <row r="5" spans="1:24" ht="23" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="42">
         <v>0</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="42">
         <f>D5+1</f>
         <v>1</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="42">
         <f t="shared" ref="F5:Q5" si="0">E5+1</f>
         <v>2</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="42">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="42">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="42">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="42">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="42">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="42">
         <f>L5+1</f>
         <v>9</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="42">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="42">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="42">
         <f>O5+1</f>
         <v>12</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="42">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="40">
         <f>Q5+1</f>
         <v>14</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="40">
         <f>R5+1</f>
         <v>15</v>
       </c>
-      <c r="T5" s="43"/>
+      <c r="T5" s="41"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
     </row>
     <row r="6" spans="1:24" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="44" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="30">
@@ -16786,7 +16845,7 @@
       <c r="T6" s="18"/>
     </row>
     <row r="7" spans="1:24" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="45" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="32">
@@ -16842,7 +16901,7 @@
     <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="46" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="34">
@@ -16902,7 +16961,7 @@
     <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="46" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="34">
@@ -16962,7 +17021,7 @@
     <row r="10" spans="1:24" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="46" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="36">
@@ -17022,7 +17081,7 @@
     <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="47" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="38">
@@ -17722,16 +17781,16 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2">
